--- a/training_forms/004_personal_training_consultation_questionnaire--training_forms.xlsx
+++ b/training_forms/004_personal_training_consultation_questionnaire--training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spouse',_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'spouse', 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'weight_loss',_'label':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'weight_loss', 'label': 'Weight Loss'}</t>
+          <t>Weight Loss</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'muscle_gain',_'label':_'muscle_gain'}</t>
+          <t>muscle_gain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'muscle_gain', 'label': 'Muscle Gain'}</t>
+          <t>Muscle Gain</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'endurance',_'label':_'endurance'}</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'endurance', 'label': 'Endurance'}</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'flexibility',_'label':_'flexibility'}</t>
+          <t>flexibility</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'flexibility', 'label': 'Flexibility'}</t>
+          <t>Flexibility</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'injury_recovery',_'label':_'injury_recovery'}</t>
+          <t>injury_recovery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'injury_recovery', 'label': 'Injury Recovery'}</t>
+          <t>Injury Recovery</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'strength',_'label':_'strength'}</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'strength', 'label': 'Strength'}</t>
+          <t>Strength</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'endurance',_'label':_'endurance'}</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'endurance', 'label': 'Endurance'}</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'power',_'label':_'power'}</t>
+          <t>agility</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'power', 'label': 'Power'}</t>
+          <t>Agility</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'agility',_'label':_'agility'}</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'agility', 'label': 'Agility'}</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>training_goals_choices</t>
+          <t>available_trainingsession_times_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'balance',_'label':_'balance'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'balance', 'label': 'Balance'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'morning',_'label':_'morning'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'morning', 'label': 'Morning'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'afternoon',_'label':_'afternoon'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'afternoon', 'label': 'Afternoon'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>available_trainingsession_times_choices</t>
+          <t>available_trainingsession_days_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'evening',_'label':_'evening'}</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'evening', 'label': 'Evening'}</t>
+          <t>Mon</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mon',_'label':_'mon'}</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'mon', 'label': 'Mon'}</t>
+          <t>Tue</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tue',_'label':_'tue'}</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'tue', 'label': 'Tue'}</t>
+          <t>Wed</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wed',_'label':_'wed'}</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'wed', 'label': 'Wed'}</t>
+          <t>Thu</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'thu',_'label':_'thu'}</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'thu', 'label': 'Thu'}</t>
+          <t>Fri</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'fri',_'label':_'fri'}</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'fri', 'label': 'Fri'}</t>
+          <t>Sat</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'sat',_'label':_'sat'}</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'sat', 'label': 'Sat'}</t>
+          <t>Sun</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>available_trainingsession_days_choices</t>
+          <t>trainingsession_duration_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'sun',_'label':_'sun'}</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'sun', 'label': 'Sun'}</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_30,_'label':_30}</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 30, 'label': 30}</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_60,_'label':_60}</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 60, 'label': 60}</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>trainingsession_duration_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_90,_'label':_90}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 90, 'label': 90}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_'parent'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'parent', 'label': 'Parent'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spouse',_'label':_'spouse'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'spouse', 'label': 'Spouse'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
